--- a/artfynd/A 49122-2021 artfynd.xlsx
+++ b/artfynd/A 49122-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49122-2021 artfynd.xlsx
+++ b/artfynd/A 49122-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,64 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96555026</v>
+        <v>96236413</v>
       </c>
       <c r="B2" t="n">
-        <v>101257</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104160</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandnäva</t>
+          <t>Svedjenäva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Geranium lanuginosum</t>
+          <t>Geranium bohemicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Lam.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mönsterås, Sm</t>
+          <t>Finsjöbrännan, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575578.0486808221</v>
+        <v>575599</v>
       </c>
       <c r="R2" t="n">
-        <v>6335328.255461412</v>
+        <v>6335337</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,22 +756,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-10-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-10-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Försiktig uppskattning av antal. Växte blandat med brandnäva.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,33 +775,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Pontus Axén</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Pontus Axén</t>
+          <t>Jesper Hansson, Erik Nordlind</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102650073</v>
+        <v>96554619</v>
       </c>
       <c r="B3" t="n">
-        <v>101246</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104160</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,33 +822,19 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Finsjö brandfält, Sm</t>
+          <t>N om Kulleberg, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575584.9834874836</v>
+        <v>575552</v>
       </c>
       <c r="R3" t="n">
-        <v>6335335.434908886</v>
+        <v>6335344</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -875,22 +861,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-03</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,64 +875,62 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Helena Lager</t>
+          <t>Pontus Axén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helena Lager</t>
+          <t>Pontus Axén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102658436</v>
+        <v>102650073</v>
       </c>
       <c r="B4" t="n">
-        <v>101257</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104160</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brandnäva</t>
+          <t>Svedjenäva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Geranium lanuginosum</t>
+          <t>Geranium bohemicum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Lam.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -970,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575584.9834874836</v>
+        <v>575585</v>
       </c>
       <c r="R4" t="n">
-        <v>6335335.434908886</v>
+        <v>6335335</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1003,19 +977,9 @@
           <t>2022-08-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,15 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102777203</v>
+        <v>102777119</v>
       </c>
       <c r="B5" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104160</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,35 +1018,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>706</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svedjenäva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Geranium bohemicum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1095,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575561.6676820596</v>
+        <v>575571</v>
       </c>
       <c r="R5" t="n">
-        <v>6335332.295276802</v>
+        <v>6335335</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1128,19 +1091,14 @@
           <t>2022-08-08</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-08-08</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Alla plantorna var samlade runt den angivna positionen. Gick en liten sväng ut på det övriga brandfältet utan att hitta några nävor.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,6 +1107,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1167,42 +1126,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102777119</v>
+        <v>96236411</v>
       </c>
       <c r="B6" t="n">
-        <v>101246</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104171</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svedjenäva</t>
+          <t>Brandnäva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Geranium bohemicum</t>
+          <t>Geranium lanuginosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Lam.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1212,24 +1166,24 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Finsjö brandfält, Sm</t>
+          <t>Finsjöbrännan, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575570.8654602371</v>
+        <v>575599</v>
       </c>
       <c r="R6" t="n">
-        <v>6335334.633739357</v>
+        <v>6335337</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1253,27 +1207,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-08-08</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-08-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Alla plantorna var samlade runt den angivna positionen. Gick en liten sväng ut på det övriga brandfältet utan att hitta några nävor.</t>
+          <t>Försiktig uppskattning av antal. Växte blandat med svedjenäva.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1289,27 +1233,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Krister Wahlström</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Krister Wahlström</t>
+          <t>Jesper Hansson, Erik Nordlind</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102777181</v>
+        <v>96555026</v>
       </c>
       <c r="B7" t="n">
-        <v>101257</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104171</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1334,36 +1273,22 @@
           <t>Lam.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Finsjö brandfält, Sm</t>
+          <t>Mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575561.6676820596</v>
+        <v>575578</v>
       </c>
       <c r="R7" t="n">
-        <v>6335332.295276802</v>
+        <v>6335328</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1387,27 +1312,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-08-08</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-08-08</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Två plantor nära varandra</t>
+          <t>2021-10-09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1416,34 +1326,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Krister Wahlström</t>
+          <t>Pontus Axén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Krister Wahlström</t>
+          <t>Pontus Axén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104947648</v>
+        <v>102658436</v>
       </c>
       <c r="B8" t="n">
-        <v>101257</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104171</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,11 +1377,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -1487,17 +1387,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Röbäcksmossen, Finsjö, Sm</t>
+          <t>Finsjö brandfält, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575591.3550111845</v>
+        <v>575585</v>
       </c>
       <c r="R8" t="n">
-        <v>6335343.689012251</v>
+        <v>6335335</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1521,27 +1421,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-07-08</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2022-08-03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-07-08</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Känd förekomst.</t>
+          <t>2022-08-03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1557,15 +1442,496 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Helena Lager</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Helena Lager</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>102777181</v>
+      </c>
+      <c r="B9" t="n">
+        <v>104171</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>707</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Brandnäva</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Geranium lanuginosum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Lam.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Finsjö brandfält, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>575562</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6335332</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-08-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-08-08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Två plantor nära varandra</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>102873503</v>
+      </c>
+      <c r="B10" t="n">
+        <v>104171</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>707</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Brandnäva</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Geranium lanuginosum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Lam.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Finsjö brandfält, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>575591</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6335320</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-08-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-08-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Återfynd.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Brandfält</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>104947648</v>
+      </c>
+      <c r="B11" t="n">
+        <v>104171</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>707</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Brandnäva</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Geranium lanuginosum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Lam.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Röbäcksmossen, Finsjö, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>575592</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6335344</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-07-08</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-07-08</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Känd förekomst.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
           <t>Niklas Hjort</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>Niklas Hjort</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>102777203</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Finsjö brandfält, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>575562</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6335332</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-08-08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-08-08</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49122-2021 artfynd.xlsx
+++ b/artfynd/A 49122-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96236413</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96554619</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102650073</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1123,6 +1143,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102777119</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1242,6 +1267,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96236411</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1341,6 +1371,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96555026</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1451,6 +1486,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102658436</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1570,6 +1610,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102777181</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1694,6 +1739,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102873503</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1823,6 +1873,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947648</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1932,8 +1987,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102777203</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>